--- a/web/public/forms/orig/o-seongeum.xlsx
+++ b/web/public/forms/orig/o-seongeum.xlsx
@@ -279,7 +279,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -291,13 +291,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="169" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -309,7 +309,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -318,7 +318,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -342,7 +342,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -748,7 +748,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="52" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="52" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="52" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="52" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="52" t="inlineStr">
@@ -4948,7 +4948,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="52" t="inlineStr">

--- a/web/public/forms/orig/o-seongeum.xlsx
+++ b/web/public/forms/orig/o-seongeum.xlsx
@@ -733,7 +733,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
